--- a/results/job_matches_2026-10-18.xlsx
+++ b/results/job_matches_2026-10-18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,17 +526,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,19 +554,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
+          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Westley Resource</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -575,21 +575,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=203d1d5d70a09d61</t>
         </is>
       </c>
     </row>
@@ -631,25 +631,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data analyst/Data Engineer</t>
+          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
+          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Engineer, ML, SMAI</t>
+          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Vibhutechinc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -798,286 +798,6 @@
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Hartford, CT, USA USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Anaheim, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer - ClickHouse</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Qualys</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Foster City, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AL, USA USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, MarTech (Remote)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Engineer- Software, AI and Data Analytics</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>American Honda Motor</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>East Liberty, OH, USA USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Vibhutechinc</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
         </is>

--- a/results/job_matches_2026-10-18.xlsx
+++ b/results/job_matches_2026-10-18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer 4, Real-time Data Platform</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Englewood, CO, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b8331b9f96dda9</t>
+          <t>https://www.indeed.com/viewjob?jk=50267e1f88400770</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Englewood, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,19 +519,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50267e1f88400770</t>
+          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Westley Resource</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -540,81 +540,81 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=203d1d5d70a09d61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Westley Resource</t>
+          <t>Retail Insight Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203d1d5d70a09d61</t>
+          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Retail Insight Ltd</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
+          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,112 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sr Engineer, ML, SMAI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boise, ID, USA USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Vibhutechinc</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-18.xlsx
+++ b/results/job_matches_2026-10-18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Westley Resource</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Englewood, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50267e1f88400770</t>
+          <t>https://www.indeed.com/viewjob?jk=203d1d5d70a09d61</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Retail Insight Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,19 +519,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Westley Resource</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -540,161 +540,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203d1d5d70a09d61</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Retail Insight Ltd</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>College Board</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Medallia</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>McLean, VA, USA USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-18.xlsx
+++ b/results/job_matches_2026-10-18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,70 +491,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Retail Insight Ltd</t>
+          <t>The Walt Disney Studios</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Burbank, CA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>College Board</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
         </is>
       </c>
     </row>
